--- a/data/defaultSSS.xlsx
+++ b/data/defaultSSS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="true"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="153">
   <si>
     <t xml:space="preserve">&lt;&lt;Project Name&gt;&gt;
 Software System Specification </t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">Details</t>
   </si>
   <si>
-    <t xml:space="preserve">Justification</t>
+    <t xml:space="preserve">Rationale / Justification</t>
   </si>
   <si>
     <t xml:space="preserve">Note</t>
@@ -397,9 +397,6 @@
 The detail of what needs to go into the requirement is dependent upon the requirement type, and is specified as part of the ECSS standard.  Further details with respect to the ECSS expected response can be found in ECSS-E-ST-40C, Annex B, Section 5 &amp; 6, 6th March 2009.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rationale / Justification</t>
-  </si>
-  <si>
     <t xml:space="preserve">It is useful to record why a specific requirement has been created.  This allows assessment and analysis if needs or conflicts arise.</t>
   </si>
   <si>
@@ -556,7 +553,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -622,6 +619,12 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -838,7 +841,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1100,6 +1103,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1230,9 +1237,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>592920</xdr:colOff>
+      <xdr:colOff>592560</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>77400</xdr:rowOff>
+      <xdr:rowOff>77040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1242,7 +1249,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11130840" y="1141920"/>
-          <a:ext cx="4192920" cy="2373840"/>
+          <a:ext cx="4192560" cy="2373480"/>
         </a:xfrm>
         <a:noFill/>
         <a:ln w="0">
@@ -1272,9 +1279,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>448920</xdr:colOff>
+      <xdr:colOff>448560</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>54720</xdr:rowOff>
+      <xdr:rowOff>54360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1284,7 +1291,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5377680" y="188640"/>
-          <a:ext cx="5294160" cy="2218680"/>
+          <a:ext cx="5293800" cy="2218320"/>
         </a:xfrm>
         <a:noFill/>
         <a:ln w="0">
@@ -1314,9 +1321,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>286920</xdr:colOff>
+      <xdr:colOff>286560</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>113760</xdr:rowOff>
+      <xdr:rowOff>113400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1326,7 +1333,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7200720" y="141120"/>
-          <a:ext cx="4048200" cy="2515680"/>
+          <a:ext cx="4047840" cy="2515320"/>
         </a:xfrm>
         <a:noFill/>
         <a:ln w="0">
@@ -1356,9 +1363,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>178920</xdr:colOff>
+      <xdr:colOff>178560</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>76320</xdr:rowOff>
+      <xdr:rowOff>75960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1368,7 +1375,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7288920" y="336960"/>
-          <a:ext cx="4648320" cy="1568160"/>
+          <a:ext cx="4647960" cy="1567800"/>
         </a:xfrm>
         <a:noFill/>
         <a:ln w="0">
@@ -1398,9 +1405,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>570600</xdr:colOff>
+      <xdr:colOff>570240</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>42120</xdr:rowOff>
+      <xdr:rowOff>41760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1410,7 +1417,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6517440" y="160920"/>
-          <a:ext cx="4582800" cy="5555520"/>
+          <a:ext cx="4582440" cy="5555160"/>
         </a:xfrm>
         <a:noFill/>
         <a:ln w="0">
@@ -1440,9 +1447,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>315720</xdr:colOff>
+      <xdr:colOff>315360</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>151200</xdr:rowOff>
+      <xdr:rowOff>150840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1452,7 +1459,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6775920" y="92880"/>
-          <a:ext cx="4701240" cy="620280"/>
+          <a:ext cx="4700880" cy="619920"/>
         </a:xfrm>
         <a:noFill/>
         <a:ln w="0">
@@ -1482,9 +1489,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>216720</xdr:colOff>
+      <xdr:colOff>216360</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>65880</xdr:rowOff>
+      <xdr:rowOff>65520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1494,7 +1501,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7496280" y="138960"/>
-          <a:ext cx="5924160" cy="2108160"/>
+          <a:ext cx="5923800" cy="2107800"/>
         </a:xfrm>
         <a:noFill/>
         <a:ln w="0">
@@ -2239,7 +2246,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -2251,21 +2258,21 @@
       <c r="I1" s="21"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="77" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
@@ -2385,21 +2392,21 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="76" t="s">
-        <v>128</v>
-      </c>
-      <c r="B24" s="76"/>
-      <c r="C24" s="76"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
-      <c r="I24" s="76"/>
+      <c r="A24" s="77" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
@@ -2412,7 +2419,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>32</v>
@@ -2420,7 +2427,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B27" s="18" t="s">
         <v>34</v>
@@ -2428,7 +2435,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B28" s="18" t="s">
         <v>36</v>
@@ -2436,7 +2443,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B29" s="18" t="s">
         <v>38</v>
@@ -2444,75 +2451,75 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="77" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="76" t="s">
-        <v>145</v>
-      </c>
-      <c r="B42" s="76"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
-      <c r="I42" s="76"/>
+      <c r="B42" s="77"/>
+      <c r="C42" s="77"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
+      <c r="I42" s="77"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B43" s="23"/>
       <c r="C43" s="23"/>
@@ -2525,35 +2532,35 @@
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="76" t="s">
+      <c r="A48" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="B48" s="76"/>
-      <c r="C48" s="76"/>
-      <c r="D48" s="76"/>
-      <c r="E48" s="76"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="76"/>
-      <c r="H48" s="76"/>
-      <c r="I48" s="76"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="77"/>
+      <c r="E48" s="77"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="77"/>
+      <c r="I48" s="77"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
@@ -2566,17 +2573,17 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -3652,10 +3659,10 @@
       <c r="C2" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="66" t="s">
         <v>80</v>
       </c>
       <c r="F2" s="65" t="s">
@@ -3771,11 +3778,11 @@
       <c r="C1" s="21"/>
     </row>
     <row r="2" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="20"/>
@@ -3790,11 +3797,11 @@
       <c r="C4" s="21"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
@@ -3808,161 +3815,161 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="70" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="374.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="73" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="70" t="s">
+      <c r="A9" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="72" t="s">
+      <c r="C9" s="73" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="71" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="72" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="71" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="71" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="C11" s="73" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="70" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="71" t="s">
+    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="72" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="70" t="s">
+      <c r="C12" s="73" t="s">
         <v>109</v>
       </c>
-      <c r="B12" s="71" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="72" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="72" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="72" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="70" t="s">
-        <v>111</v>
-      </c>
-      <c r="B13" s="71" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="72" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="70" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="71" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="72" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="70" t="s">
+      <c r="C15" s="73" t="s">
         <v>115</v>
       </c>
-      <c r="B15" s="71" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="71" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="72" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="70" t="s">
+      <c r="C16" s="73" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="71" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="72" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="70" t="s">
+      <c r="C17" s="73" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="71" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C18" s="73" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="70" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="71" t="s">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="74" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="75" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="72" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="73" t="s">
+      <c r="C19" s="76" t="s">
         <v>122</v>
-      </c>
-      <c r="B19" s="74" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="75" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="105.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="66" t="s">
-        <v>125</v>
-      </c>
-      <c r="B22" s="66"/>
-      <c r="C22" s="66"/>
+      <c r="A22" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="6">
